--- a/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>NBY</t>
   </si>
@@ -656,291 +656,304 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F8" s="3">
         <v>3300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="P8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="S8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="X8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Z8" s="3">
         <v>3100</v>
       </c>
-      <c r="G8" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2600</v>
-      </c>
-      <c r="L8" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M8" s="3">
-        <v>4800</v>
-      </c>
-      <c r="N8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="O8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>4000</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="S8" s="3">
-        <v>1700</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1600</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1500</v>
-      </c>
-      <c r="W8" s="3">
-        <v>3600</v>
-      </c>
-      <c r="X8" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>6300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4100</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>4100</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>3700</v>
       </c>
       <c r="AE8" s="3">
         <v>4100</v>
       </c>
       <c r="AF8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AH8" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F9" s="3">
         <v>1400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2300</v>
       </c>
-      <c r="F9" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>700</v>
+      </c>
+      <c r="I9" s="3">
         <v>1900</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1800</v>
       </c>
       <c r="J9" s="3">
         <v>1500</v>
       </c>
       <c r="K9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M9" s="3">
         <v>1200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1500</v>
-      </c>
-      <c r="N9" s="3">
-        <v>500</v>
-      </c>
-      <c r="O9" s="3">
-        <v>800</v>
       </c>
       <c r="P9" s="3">
         <v>500</v>
       </c>
       <c r="Q9" s="3">
+        <v>800</v>
+      </c>
+      <c r="R9" s="3">
+        <v>500</v>
+      </c>
+      <c r="S9" s="3">
         <v>2000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>400</v>
-      </c>
-      <c r="U9" s="3">
-        <v>400</v>
-      </c>
-      <c r="V9" s="3">
-        <v>300</v>
       </c>
       <c r="W9" s="3">
         <v>400</v>
@@ -949,123 +962,135 @@
         <v>300</v>
       </c>
       <c r="Y9" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z9" s="3">
         <v>300</v>
       </c>
       <c r="AA9" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC9" s="3">
         <v>1000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>700</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>600</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>800</v>
       </c>
       <c r="AF9" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E10" s="3">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="F10" s="3">
         <v>1900</v>
       </c>
       <c r="G10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I10" s="3">
         <v>1700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1100</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>1400</v>
       </c>
       <c r="V10" s="3">
         <v>1200</v>
       </c>
       <c r="W10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y10" s="3">
         <v>3200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>5300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>3300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1113,14 +1140,14 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
       <c r="J12" s="3">
         <v>0</v>
       </c>
@@ -1140,17 +1167,17 @@
         <v>0</v>
       </c>
       <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>100</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
       <c r="T12" s="3">
         <v>0</v>
       </c>
@@ -1158,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="V12" s="3">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
         <v>100</v>
-      </c>
-      <c r="W12" s="3">
-        <v>100</v>
-      </c>
-      <c r="X12" s="3">
-        <v>0</v>
       </c>
       <c r="Y12" s="3">
         <v>100</v>
@@ -1176,7 +1203,7 @@
         <v>100</v>
       </c>
       <c r="AB12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="3">
         <v>100</v>
@@ -1185,13 +1212,19 @@
         <v>100</v>
       </c>
       <c r="AE12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG12" s="3">
         <v>200</v>
       </c>
-      <c r="AF12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,28 +1315,34 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>19</v>
+      <c r="E14" s="3">
+        <v>2600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="3">
-        <v>6700</v>
+      <c r="G14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>19</v>
+      <c r="I14" s="3">
+        <v>6700</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>19</v>
@@ -1314,41 +1353,41 @@
       <c r="L14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>19</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>100</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>19</v>
@@ -1356,11 +1395,11 @@
       <c r="Z14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F17" s="3">
         <v>4400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
-        <v>4900</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I17" s="3">
         <v>13100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>5800</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5700</v>
       </c>
       <c r="K17" s="3">
         <v>5800</v>
       </c>
       <c r="L17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="M17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>8100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>5200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>4900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>5300</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>5900</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>6300</v>
       </c>
       <c r="AC17" s="3">
         <v>5900</v>
       </c>
       <c r="AD17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AF17" s="3">
         <v>7500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>6200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-1800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="AF18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="AH18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>400</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>-2100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,41 +1780,43 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-700</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
         <v>-700</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="G20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>3100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1757,150 +1824,162 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>500</v>
       </c>
       <c r="Z20" s="3">
         <v>300</v>
       </c>
       <c r="AA20" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-1700</v>
+        <v>-3100</v>
       </c>
       <c r="E21" s="3">
-        <v>-2000</v>
+        <v>-4100</v>
       </c>
       <c r="F21" s="3">
         <v>-1700</v>
       </c>
       <c r="G21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-8100</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-4500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-4100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1931,11 +2010,11 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>19</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>19</v>
@@ -1949,27 +2028,27 @@
       <c r="R22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U22" s="3">
         <v>300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3" t="s">
+      <c r="Y22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
@@ -1991,181 +2070,193 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-8200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-2200</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
       </c>
       <c r="K23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-4200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-8200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2200</v>
       </c>
       <c r="J26" s="3">
         <v>-100</v>
       </c>
       <c r="K26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-2700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-4200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>13300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="X27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>13300</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="AF27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-1600</v>
       </c>
-      <c r="S27" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>13300</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,31 +2658,37 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>-400</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2599,32 +2720,32 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>19</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AA29" s="3">
-        <v>-12500</v>
+      <c r="AA29" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>19</v>
+      <c r="AC29" s="3">
+        <v>-12500</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>19</v>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,41 +2952,47 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
         <v>700</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G32" s="3">
+        <v>700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-3100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2861,150 +3000,162 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-500</v>
       </c>
       <c r="Z32" s="3">
         <v>-300</v>
       </c>
       <c r="AA32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-5800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-4200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-5800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-4200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F41" s="3">
         <v>3500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>13400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>8800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>6900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>9000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>5200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>6800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>8300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>6100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>5700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>7400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>9500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,82 +3715,88 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>800</v>
+      </c>
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>3400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2000</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>2200</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>3600</v>
       </c>
       <c r="AB43" s="3">
         <v>2200</v>
@@ -3620,78 +3805,84 @@
         <v>3600</v>
       </c>
       <c r="AD43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AF43" s="3">
         <v>2300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>2100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F44" s="3">
         <v>3500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>3800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>4100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>900</v>
-      </c>
-      <c r="O44" s="3">
-        <v>600</v>
-      </c>
-      <c r="P44" s="3">
-        <v>800</v>
       </c>
       <c r="Q44" s="3">
         <v>600</v>
       </c>
       <c r="R44" s="3">
+        <v>800</v>
+      </c>
+      <c r="S44" s="3">
         <v>600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
+        <v>600</v>
+      </c>
+      <c r="U44" s="3">
         <v>500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>700</v>
-      </c>
-      <c r="V44" s="3">
-        <v>400</v>
-      </c>
-      <c r="W44" s="3">
-        <v>300</v>
       </c>
       <c r="X44" s="3">
         <v>400</v>
@@ -3700,42 +3891,48 @@
         <v>300</v>
       </c>
       <c r="Z44" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB44" s="3">
         <v>500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>400</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>600</v>
       </c>
       <c r="H45" s="3">
         <v>500</v>
@@ -3744,168 +3941,180 @@
         <v>600</v>
       </c>
       <c r="J45" s="3">
+        <v>500</v>
+      </c>
+      <c r="K45" s="3">
+        <v>600</v>
+      </c>
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>700</v>
-      </c>
-      <c r="M45" s="3">
-        <v>600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>800</v>
       </c>
       <c r="O45" s="3">
         <v>600</v>
       </c>
       <c r="P45" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Q45" s="3">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="R45" s="3">
         <v>700</v>
       </c>
       <c r="S45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T45" s="3">
+        <v>700</v>
+      </c>
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1700</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>900</v>
       </c>
       <c r="AD45" s="3">
         <v>1000</v>
       </c>
       <c r="AE45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG45" s="3">
         <v>2000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F46" s="3">
         <v>8200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>9900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>11300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>13200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>12800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>13100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>14200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>16000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>11900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>7900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>9400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>12500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>7500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>8600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>9500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>10800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>12800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>9000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>9900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>11000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>11500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>14500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,132 +4205,144 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F48" s="3">
         <v>1600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>400</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>500</v>
       </c>
       <c r="AC48" s="3">
         <v>500</v>
       </c>
       <c r="AD48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF48" s="3">
         <v>400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>2500</v>
-      </c>
-      <c r="E49" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F49" s="3">
-        <v>2600</v>
       </c>
       <c r="G49" s="3">
         <v>2600</v>
       </c>
       <c r="H49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J49" s="3">
         <v>9500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>9500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>9600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>9700</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>19</v>
@@ -4132,11 +4353,11 @@
       <c r="P49" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4382,19 +4621,19 @@
         <v>500</v>
       </c>
       <c r="H52" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I52" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
       </c>
       <c r="K52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>500</v>
@@ -4427,10 +4666,10 @@
         <v>500</v>
       </c>
       <c r="W52" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="X52" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Y52" s="3">
         <v>600</v>
@@ -4448,16 +4687,22 @@
         <v>600</v>
       </c>
       <c r="AD52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF52" s="3">
         <v>700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F54" s="3">
         <v>12900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>14800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>16400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>22400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>21500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>24800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>24000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>12200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>13600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>15200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>17100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>13300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>9500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>11200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>14600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>9900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>9700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>9400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>10400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>11700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>13800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>10100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>11100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>12100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>12700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>15400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,118 +4967,126 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1100</v>
       </c>
       <c r="H57" s="3">
         <v>1100</v>
       </c>
       <c r="I57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>800</v>
-      </c>
-      <c r="O57" s="3">
-        <v>300</v>
       </c>
       <c r="P57" s="3">
         <v>800</v>
       </c>
       <c r="Q57" s="3">
+        <v>300</v>
+      </c>
+      <c r="R57" s="3">
+        <v>800</v>
+      </c>
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>500</v>
-      </c>
-      <c r="U57" s="3">
-        <v>400</v>
       </c>
       <c r="V57" s="3">
         <v>500</v>
       </c>
       <c r="W57" s="3">
+        <v>400</v>
+      </c>
+      <c r="X57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -4827,46 +5094,46 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>100</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3000</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1000</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>19</v>
+      <c r="X58" s="3">
+        <v>1000</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>19</v>
@@ -4874,11 +5141,11 @@
       <c r="Z58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -4892,192 +5159,210 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2200</v>
-      </c>
-      <c r="O59" s="3">
-        <v>2500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>2100</v>
       </c>
       <c r="Q59" s="3">
         <v>2500</v>
       </c>
       <c r="R59" s="3">
-        <v>2700</v>
+        <v>2100</v>
       </c>
       <c r="S59" s="3">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="T59" s="3">
         <v>2700</v>
       </c>
       <c r="U59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W59" s="3">
         <v>3000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>3900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>3300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>4500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>4900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>3800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>3500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>3900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>5500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>5400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>3200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>5000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>4700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>4300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>4300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5133,17 +5418,17 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>2800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5168,100 +5453,112 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E62" s="3">
         <v>1400</v>
       </c>
       <c r="F62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H62" s="3">
         <v>1500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>4900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>10400</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>8000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2500</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>4100</v>
       </c>
       <c r="AD62" s="3">
         <v>4000</v>
       </c>
       <c r="AE62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AF62" s="3">
         <v>4000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AH62" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F66" s="3">
         <v>5800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5900</v>
-      </c>
-      <c r="G66" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>8600</v>
       </c>
       <c r="I66" s="3">
         <v>5800</v>
       </c>
       <c r="J66" s="3">
+        <v>8600</v>
+      </c>
+      <c r="K66" s="3">
+        <v>5800</v>
+      </c>
+      <c r="L66" s="3">
         <v>7000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>13800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>10200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>11100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>8200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>8600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>4300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>4300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>5000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>7500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>9200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>8900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>8300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>8300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,41 +6175,47 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E70" s="3">
         <v>2000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G70" s="3">
         <v>2100</v>
       </c>
-      <c r="F70" s="3">
+      <c r="H70" s="3">
         <v>3000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="I70" s="3">
         <v>3000</v>
-      </c>
-      <c r="H70" s="3">
-        <v>600</v>
-      </c>
-      <c r="I70" s="3">
-        <v>600</v>
       </c>
       <c r="J70" s="3">
         <v>600</v>
       </c>
       <c r="K70" s="3">
+        <v>600</v>
+      </c>
+      <c r="L70" s="3">
+        <v>600</v>
+      </c>
+      <c r="M70" s="3">
         <v>700</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -5900,14 +6235,14 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>600</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-178400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-174800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-165700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-163900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-159900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-158200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-149900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-144200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-142000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-141900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-141700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-139400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-137600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-136100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-134300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-131100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-126600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-125000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-122300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-122100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-119500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-115000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-113700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-112200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-110600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-111100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-111900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-109400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-107700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-103700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-102000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F76" s="3">
         <v>5100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>13200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>15200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>17100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>12300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13900</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R76" s="3">
-        <v>-300</v>
       </c>
       <c r="S76" s="3">
         <v>1000</v>
       </c>
       <c r="T76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V76" s="3">
         <v>2900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>5000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>6100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>7400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>8900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>2600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>3200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>7100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-5800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-4200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,13 +7200,15 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -6835,10 +7232,10 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -6871,17 +7268,17 @@
         <v>0</v>
       </c>
       <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-1600</v>
-      </c>
       <c r="G89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-1400</v>
       </c>
       <c r="P89" s="3">
         <v>-1400</v>
       </c>
       <c r="Q89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="S89" s="3">
         <v>-1000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-3200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7501,14 +7942,14 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -7524,20 +7965,20 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>19</v>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -7561,10 +8002,10 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
@@ -7573,10 +8014,16 @@
         <v>-100</v>
       </c>
       <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,13 +8212,19 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -7777,23 +8236,23 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-12000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -7837,10 +8296,10 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD94" s="3">
         <v>-100</v>
@@ -7849,10 +8308,16 @@
         <v>-100</v>
       </c>
       <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8738,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>14800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1800</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>6000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>4100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>6900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>2500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>3000</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>5600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>4600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>5400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>5100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>5900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>NBY</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3300</v>
       </c>
-      <c r="G8" s="3">
-        <v>4600</v>
-      </c>
       <c r="H8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I8" s="3">
         <v>2300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6300</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>4100</v>
       </c>
       <c r="AE8" s="3">
         <v>4100</v>
       </c>
       <c r="AF8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AG8" s="3">
         <v>3700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -902,195 +909,201 @@
         <v>800</v>
       </c>
       <c r="E9" s="3">
+        <v>800</v>
+      </c>
+      <c r="F9" s="3">
         <v>1900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1400</v>
       </c>
-      <c r="G9" s="3">
-        <v>2300</v>
-      </c>
       <c r="H9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2000</v>
-      </c>
-      <c r="T9" s="3">
-        <v>600</v>
       </c>
       <c r="U9" s="3">
         <v>600</v>
       </c>
       <c r="V9" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="W9" s="3">
         <v>400</v>
       </c>
       <c r="X9" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y9" s="3">
         <v>300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="E10" s="3">
         <v>1800</v>
       </c>
       <c r="F10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G10" s="3">
         <v>1900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K10" s="3">
         <v>2300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O10" s="3">
         <v>1600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="P10" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S10" s="3">
         <v>1700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="T10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AB10" s="3">
         <v>2300</v>
       </c>
-      <c r="K10" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="AC10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AH10" s="3">
         <v>3300</v>
       </c>
-      <c r="P10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="S10" s="3">
-        <v>2000</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="U10" s="3">
-        <v>1100</v>
-      </c>
-      <c r="V10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="W10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>3200</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AI10" s="3">
         <v>2800</v>
       </c>
-      <c r="AA10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>2600</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>5300</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>3600</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>3400</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>3100</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>3300</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1146,11 +1160,11 @@
         <v>0</v>
       </c>
       <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
       <c r="K12" s="3">
         <v>0</v>
       </c>
@@ -1173,13 +1187,13 @@
         <v>0</v>
       </c>
       <c r="R12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S12" s="3">
         <v>100</v>
       </c>
       <c r="T12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12" s="3">
         <v>0</v>
@@ -1191,22 +1205,22 @@
         <v>0</v>
       </c>
       <c r="X12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3">
         <v>100</v>
       </c>
       <c r="Z12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
         <v>100</v>
       </c>
-      <c r="AB12" s="3">
-        <v>0</v>
-      </c>
       <c r="AC12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="3">
         <v>100</v>
@@ -1218,13 +1232,16 @@
         <v>100</v>
       </c>
       <c r="AG12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH12" s="3">
         <v>200</v>
       </c>
-      <c r="AH12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,31 +1338,34 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>19</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>900</v>
+      </c>
+      <c r="F14" s="3">
         <v>2600</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6700</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1359,8 +1379,8 @@
       <c r="N14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1368,8 +1388,8 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>19</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>19</v>
@@ -1377,8 +1397,8 @@
       <c r="T14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1387,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>100</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>19</v>
@@ -1401,8 +1421,8 @@
       <c r="AB14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E17" s="3">
         <v>5100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4400</v>
       </c>
-      <c r="G17" s="3">
-        <v>6000</v>
-      </c>
       <c r="H17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I17" s="3">
         <v>3700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="X18" s="3">
         <v>-1400</v>
       </c>
-      <c r="I18" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="Y18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="AC18" s="3">
         <v>-2400</v>
       </c>
-      <c r="M18" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="AD18" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-2200</v>
       </c>
-      <c r="V18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>-2100</v>
       </c>
       <c r="AH18" s="3">
         <v>-2100</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>-2100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1782,16 +1815,17 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-700</v>
       </c>
       <c r="F20" s="3">
         <v>-700</v>
@@ -1800,26 +1834,26 @@
         <v>-700</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1830,156 +1864,162 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8100</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2016,8 +2056,8 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>19</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>19</v>
@@ -2034,24 +2074,24 @@
       <c r="T22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U22" s="3">
-        <v>300</v>
+      <c r="U22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="V22" s="3">
         <v>300</v>
       </c>
       <c r="W22" s="3">
+        <v>300</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3" t="s">
+      <c r="Z22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
@@ -2076,106 +2116,112 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-2000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2251,15 +2297,15 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-      <c r="AB24" s="3" t="s">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-12500</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
-        <v>-2000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>13300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="W27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>13300</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="AH27" s="3">
         <v>-1600</v>
       </c>
-      <c r="U27" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>13300</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,16 +2722,19 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-100</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>19</v>
@@ -2682,16 +2743,16 @@
         <v>19</v>
       </c>
       <c r="H29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I29" s="3">
         <v>-400</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2726,17 +2787,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>19</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>19</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>19</v>
@@ -2744,11 +2805,11 @@
       <c r="AB29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-12500</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>19</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,16 +3025,19 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>700</v>
       </c>
       <c r="F32" s="3">
         <v>700</v>
@@ -2976,26 +3046,26 @@
         <v>700</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3006,156 +3076,162 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5400</v>
-      </c>
-      <c r="J41" s="3">
-        <v>3900</v>
       </c>
       <c r="K41" s="3">
         <v>3900</v>
       </c>
       <c r="L41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="M41" s="3">
         <v>5600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>9500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>1100</v>
       </c>
       <c r="R43" s="3">
         <v>1100</v>
       </c>
       <c r="S43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T43" s="3">
         <v>1400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1100</v>
-      </c>
-      <c r="V43" s="3">
-        <v>1500</v>
       </c>
       <c r="W43" s="3">
         <v>1500</v>
       </c>
       <c r="X43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y43" s="3">
         <v>2400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2300</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>2100</v>
       </c>
       <c r="AH43" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3828,293 +3924,302 @@
         <v>700</v>
       </c>
       <c r="E44" s="3">
+        <v>700</v>
+      </c>
+      <c r="F44" s="3">
         <v>2900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4100</v>
-      </c>
-      <c r="K44" s="3">
-        <v>3800</v>
       </c>
       <c r="L44" s="3">
         <v>3800</v>
       </c>
       <c r="M44" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N44" s="3">
         <v>3200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>800</v>
-      </c>
-      <c r="S44" s="3">
-        <v>600</v>
       </c>
       <c r="T44" s="3">
         <v>600</v>
       </c>
       <c r="U44" s="3">
+        <v>600</v>
+      </c>
+      <c r="V44" s="3">
         <v>500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>300</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>500</v>
       </c>
       <c r="AC44" s="3">
         <v>500</v>
       </c>
       <c r="AD44" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE44" s="3">
         <v>600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
       </c>
       <c r="F45" s="3">
+        <v>400</v>
+      </c>
+      <c r="G45" s="3">
         <v>300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
       </c>
       <c r="H45" s="3">
         <v>500</v>
       </c>
       <c r="I45" s="3">
+        <v>500</v>
+      </c>
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>800</v>
       </c>
       <c r="M45" s="3">
         <v>800</v>
       </c>
       <c r="N45" s="3">
+        <v>800</v>
+      </c>
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E46" s="3">
         <v>3600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,88 +4316,91 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>500</v>
       </c>
       <c r="Q48" s="3">
         <v>500</v>
       </c>
       <c r="R48" s="3">
+        <v>500</v>
+      </c>
+      <c r="S48" s="3">
         <v>600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>300</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>400</v>
       </c>
       <c r="AB48" s="3">
         <v>400</v>
       </c>
       <c r="AC48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AD48" s="3">
         <v>500</v>
@@ -4301,30 +4409,33 @@
         <v>500</v>
       </c>
       <c r="AF48" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AG48" s="3">
         <v>400</v>
       </c>
       <c r="AH48" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI48" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
+      <c r="E49" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>2500</v>
-      </c>
-      <c r="G49" s="3">
-        <v>2600</v>
       </c>
       <c r="H49" s="3">
         <v>2600</v>
@@ -4333,19 +4444,19 @@
         <v>2600</v>
       </c>
       <c r="J49" s="3">
-        <v>9500</v>
+        <v>2600</v>
       </c>
       <c r="K49" s="3">
         <v>9500</v>
       </c>
       <c r="L49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="M49" s="3">
         <v>9600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9700</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>19</v>
@@ -4359,8 +4470,8 @@
       <c r="R49" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4627,7 +4747,7 @@
         <v>500</v>
       </c>
       <c r="J52" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
@@ -4636,7 +4756,7 @@
         <v>200</v>
       </c>
       <c r="M52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>500</v>
@@ -4672,7 +4792,7 @@
         <v>500</v>
       </c>
       <c r="Y52" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Z52" s="3">
         <v>600</v>
@@ -4693,16 +4813,19 @@
         <v>600</v>
       </c>
       <c r="AF52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG52" s="3">
         <v>700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E54" s="3">
         <v>5400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,25 +5099,26 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E57" s="3">
         <v>1100</v>
       </c>
       <c r="F57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1100</v>
       </c>
       <c r="I57" s="3">
         <v>1100</v>
@@ -4996,100 +5127,103 @@
         <v>1100</v>
       </c>
       <c r="K57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>600</v>
       </c>
       <c r="Z57" s="3">
         <v>600</v>
       </c>
       <c r="AA57" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AB57" s="3">
         <v>300</v>
       </c>
       <c r="AC57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="I58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -5100,10 +5234,10 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>19</v>
@@ -5111,32 +5245,32 @@
       <c r="P58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3000</v>
       </c>
-      <c r="W58" s="3" t="s">
+      <c r="X58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>19</v>
@@ -5147,8 +5281,8 @@
       <c r="AB58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5165,61 +5299,64 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1500</v>
-      </c>
-      <c r="O59" s="3">
-        <v>2200</v>
       </c>
       <c r="P59" s="3">
         <v>2200</v>
       </c>
       <c r="Q59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R59" s="3">
         <v>2500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2500</v>
-      </c>
-      <c r="T59" s="3">
-        <v>2700</v>
       </c>
       <c r="U59" s="3">
         <v>2700</v>
@@ -5228,141 +5365,147 @@
         <v>2700</v>
       </c>
       <c r="W59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X59" s="3">
         <v>3000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E60" s="3">
         <v>3900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>3700</v>
       </c>
       <c r="K60" s="3">
         <v>3700</v>
       </c>
       <c r="L60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M60" s="3">
         <v>4800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4700</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>4300</v>
       </c>
       <c r="AG60" s="3">
         <v>4300</v>
       </c>
       <c r="AH60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AI60" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5424,14 +5567,14 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>2800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1200</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5459,44 +5602,47 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10400</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
@@ -5504,61 +5650,64 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4100</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>4000</v>
       </c>
       <c r="AG62" s="3">
         <v>4000</v>
       </c>
       <c r="AH62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AI62" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4400</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>4300</v>
       </c>
       <c r="AA66" s="3">
         <v>4300</v>
       </c>
       <c r="AB66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AC66" s="3">
         <v>5000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8900</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>8300</v>
       </c>
       <c r="AG66" s="3">
         <v>8300</v>
       </c>
       <c r="AH66" s="3">
+        <v>8300</v>
+      </c>
+      <c r="AI66" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,31 +6346,34 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
         <v>1500</v>
-      </c>
-      <c r="E70" s="3">
-        <v>2000</v>
       </c>
       <c r="F70" s="3">
         <v>2000</v>
       </c>
       <c r="G70" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H70" s="3">
         <v>2100</v>
-      </c>
-      <c r="H70" s="3">
-        <v>3000</v>
       </c>
       <c r="I70" s="3">
         <v>3000</v>
       </c>
       <c r="J70" s="3">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="K70" s="3">
         <v>600</v>
@@ -6214,11 +6382,11 @@
         <v>600</v>
       </c>
       <c r="M70" s="3">
+        <v>600</v>
+      </c>
+      <c r="N70" s="3">
         <v>700</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -6241,11 +6409,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>600</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-180000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-178400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-174800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-165700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-163900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-159900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-158200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-149900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-144200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-142000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-141900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-141700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-139400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-137600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-136100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-134300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-131100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-126600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-125000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-122300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-122100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-119500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-115000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-113700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-112200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-110600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-111100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-111900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-109400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-107700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-103700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-102000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7211,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -7238,7 +7437,7 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -7274,13 +7473,13 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="3">
         <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,49 +8004,52 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
-        <v>-400</v>
-      </c>
       <c r="G89" s="3">
-        <v>-2300</v>
+        <v>-900</v>
       </c>
       <c r="H89" s="3">
-        <v>-1200</v>
+        <v>-1700</v>
       </c>
       <c r="I89" s="3">
         <v>-1200</v>
       </c>
       <c r="J89" s="3">
-        <v>-1700</v>
+        <v>-1200</v>
       </c>
       <c r="K89" s="3">
         <v>-1700</v>
       </c>
       <c r="L89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-1400</v>
       </c>
       <c r="Q89" s="3">
         <v>-1400</v>
@@ -7841,55 +8058,58 @@
         <v>-1400</v>
       </c>
       <c r="S89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T89" s="3">
         <v>-1000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7948,11 +8169,11 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -7971,8 +8192,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>19</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>19</v>
@@ -7980,8 +8201,8 @@
       <c r="T91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8008,7 +8229,7 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE91" s="3">
         <v>-100</v>
@@ -8020,10 +8241,13 @@
         <v>-100</v>
       </c>
       <c r="AH91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,17 +8445,20 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>1100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -8242,20 +8472,20 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-12000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -8302,7 +8532,7 @@
         <v>0</v>
       </c>
       <c r="AD94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE94" s="3">
         <v>-100</v>
@@ -8314,10 +8544,13 @@
         <v>-100</v>
       </c>
       <c r="AH94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,77 +8987,80 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>3000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>14800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1800</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>6000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3000</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -8822,28 +9068,31 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>5600</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>100</v>
       </c>
       <c r="AD100" s="3">
         <v>100</v>
       </c>
       <c r="AE100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>5900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>NBY</t>
   </si>
@@ -656,151 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -808,100 +812,103 @@
         <v>2400</v>
       </c>
       <c r="E8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F8" s="3">
         <v>2600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N8" s="3">
         <v>3300</v>
       </c>
-      <c r="H8" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="O8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="P8" s="3">
         <v>2300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="Q8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="R8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA8" s="3">
         <v>3600</v>
       </c>
-      <c r="K8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3700</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2600</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2300</v>
-      </c>
-      <c r="P8" s="3">
-        <v>4800</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="S8" s="3">
-        <v>2200</v>
-      </c>
-      <c r="T8" s="3">
-        <v>4000</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1700</v>
-      </c>
-      <c r="W8" s="3">
-        <v>1600</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>3600</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6300</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>4100</v>
       </c>
       <c r="AF8" s="3">
         <v>4100</v>
       </c>
       <c r="AG8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AH8" s="3">
         <v>3700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -912,97 +919,100 @@
         <v>800</v>
       </c>
       <c r="F9" s="3">
+        <v>800</v>
+      </c>
+      <c r="G9" s="3">
         <v>1900</v>
       </c>
-      <c r="G9" s="3">
-        <v>1400</v>
-      </c>
       <c r="H9" s="3">
+        <v>800</v>
+      </c>
+      <c r="I9" s="3">
         <v>1800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2000</v>
-      </c>
-      <c r="U9" s="3">
-        <v>600</v>
       </c>
       <c r="V9" s="3">
         <v>600</v>
       </c>
       <c r="W9" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="X9" s="3">
         <v>400</v>
       </c>
       <c r="Y9" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z9" s="3">
         <v>300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1010,100 +1020,103 @@
         <v>1600</v>
       </c>
       <c r="E10" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="F10" s="3">
         <v>1800</v>
       </c>
       <c r="G10" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="H10" s="3">
         <v>1700</v>
       </c>
       <c r="I10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J10" s="3">
         <v>1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1163,11 +1177,11 @@
         <v>0</v>
       </c>
       <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
       <c r="L12" s="3">
         <v>0</v>
       </c>
@@ -1190,13 +1204,13 @@
         <v>0</v>
       </c>
       <c r="S12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T12" s="3">
         <v>100</v>
       </c>
       <c r="U12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12" s="3">
         <v>0</v>
@@ -1208,22 +1222,22 @@
         <v>0</v>
       </c>
       <c r="Y12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3">
         <v>100</v>
       </c>
       <c r="AA12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3">
         <v>100</v>
       </c>
-      <c r="AC12" s="3">
-        <v>0</v>
-      </c>
       <c r="AD12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="3">
         <v>100</v>
@@ -1235,13 +1249,16 @@
         <v>100</v>
       </c>
       <c r="AH12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI12" s="3">
         <v>200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1350,25 +1370,25 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
+        <v>800</v>
+      </c>
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6700</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>19</v>
@@ -1382,8 +1402,8 @@
       <c r="O14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1391,8 +1411,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>19</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>19</v>
@@ -1400,8 +1420,8 @@
       <c r="U14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1410,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>100</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>19</v>
@@ -1424,8 +1444,8 @@
       <c r="AC14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1442,8 +1462,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1457,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,8 +1603,9 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1586,100 +1613,103 @@
         <v>3500</v>
       </c>
       <c r="E17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4500</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K17" s="3">
+        <v>13100</v>
+      </c>
+      <c r="L17" s="3">
+        <v>4300</v>
+      </c>
+      <c r="M17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="N17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="O17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="P17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="R17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="U17" s="3">
         <v>5100</v>
       </c>
-      <c r="F17" s="3">
-        <v>7100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>13100</v>
-      </c>
-      <c r="K17" s="3">
-        <v>4300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>5800</v>
-      </c>
-      <c r="M17" s="3">
-        <v>5700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>5800</v>
-      </c>
-      <c r="O17" s="3">
-        <v>4600</v>
-      </c>
-      <c r="P17" s="3">
-        <v>8100</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="V17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="X17" s="3">
         <v>3300</v>
       </c>
-      <c r="R17" s="3">
-        <v>3600</v>
-      </c>
-      <c r="S17" s="3">
-        <v>4200</v>
-      </c>
-      <c r="T17" s="3">
-        <v>5100</v>
-      </c>
-      <c r="U17" s="3">
-        <v>3400</v>
-      </c>
-      <c r="V17" s="3">
-        <v>3900</v>
-      </c>
-      <c r="W17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1687,100 +1717,103 @@
         <v>-1100</v>
       </c>
       <c r="E18" s="3">
-        <v>-2500</v>
+        <v>-1100</v>
       </c>
       <c r="F18" s="3">
-        <v>-3400</v>
+        <v>-1600</v>
       </c>
       <c r="G18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="U18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="V18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-1400</v>
       </c>
-      <c r="J18" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="Z18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="AD18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="AE18" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-2200</v>
       </c>
-      <c r="W18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>400</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>-2100</v>
       </c>
       <c r="AI18" s="3">
         <v>-2100</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>-2100</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,233 +1849,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>-500</v>
+      <c r="D20" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E20" s="3">
-        <v>-600</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>800</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>300</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="Z20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>3100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="AC20" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>300</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AI20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
-        <v>300</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>400</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>500</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-1600</v>
+        <v>-1100</v>
       </c>
       <c r="E21" s="3">
-        <v>-3100</v>
+        <v>-1200</v>
       </c>
       <c r="F21" s="3">
-        <v>-4100</v>
+        <v>-1800</v>
       </c>
       <c r="G21" s="3">
-        <v>-1600</v>
+        <v>-1500</v>
       </c>
       <c r="H21" s="3">
-        <v>-1700</v>
+        <v>-700</v>
       </c>
       <c r="I21" s="3">
         <v>-1300</v>
       </c>
       <c r="J21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-8100</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-2000</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>-100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2059,8 +2099,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>19</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>19</v>
@@ -2077,24 +2117,24 @@
       <c r="U22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V22" s="3">
-        <v>300</v>
+      <c r="V22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="W22" s="3">
         <v>300</v>
       </c>
       <c r="X22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3" t="s">
+      <c r="AA22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
@@ -2119,132 +2159,138 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="S23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="T23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-1700</v>
       </c>
-      <c r="I23" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="AH23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>800</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AH23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2300,15 +2346,15 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="S26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="T26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="W26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>13300</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-1700</v>
       </c>
-      <c r="I26" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="AH26" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-1600</v>
       </c>
-      <c r="V26" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>13300</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="W27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
-        <v>-9200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="X27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>13300</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-3700</v>
       </c>
-      <c r="I27" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>13300</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AI27" s="3">
-        <v>-3700</v>
-      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2734,28 +2795,28 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>19</v>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I29" s="3">
         <v>-300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-400</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2790,17 +2851,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>19</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>19</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>19</v>
@@ -2808,11 +2869,11 @@
       <c r="AC29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-12500</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>19</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>500</v>
+      <c r="D32" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E32" s="3">
-        <v>600</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="V32" s="3">
+        <v>100</v>
+      </c>
+      <c r="W32" s="3">
+        <v>200</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="Y32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
-        <v>700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="Z32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>3400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>100</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="AC32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="X32" s="3">
-        <v>700</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AI32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>200</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
-        <v>-3600</v>
-      </c>
       <c r="F33" s="3">
-        <v>-9200</v>
+        <v>-3200</v>
       </c>
       <c r="G33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="S33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="W33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-4000</v>
       </c>
-      <c r="I33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="AI33" s="3">
         <v>-1600</v>
       </c>
-      <c r="V33" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>800</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
-        <v>-3600</v>
-      </c>
       <c r="F35" s="3">
-        <v>-9200</v>
+        <v>-3200</v>
       </c>
       <c r="G35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="S35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="W35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-4000</v>
       </c>
-      <c r="I35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="AI35" s="3">
         <v>-1600</v>
       </c>
-      <c r="V35" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>800</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,8 +3698,9 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3621,100 +3708,103 @@
         <v>800</v>
       </c>
       <c r="E41" s="3">
+        <v>800</v>
+      </c>
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5400</v>
-      </c>
-      <c r="K41" s="3">
-        <v>3900</v>
       </c>
       <c r="L41" s="3">
         <v>3900</v>
       </c>
       <c r="M41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N41" s="3">
         <v>5600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>9500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,311 +3904,323 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
-      </c>
-      <c r="R43" s="3">
-        <v>1100</v>
       </c>
       <c r="S43" s="3">
         <v>1100</v>
       </c>
       <c r="T43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U43" s="3">
         <v>1400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1100</v>
-      </c>
-      <c r="W43" s="3">
-        <v>1500</v>
       </c>
       <c r="X43" s="3">
         <v>1500</v>
       </c>
       <c r="Y43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z43" s="3">
         <v>2400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2300</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>2100</v>
       </c>
       <c r="AI43" s="3">
         <v>2100</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>2100</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E44" s="3">
         <v>700</v>
       </c>
       <c r="F44" s="3">
-        <v>2900</v>
+        <v>700</v>
       </c>
       <c r="G44" s="3">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="H44" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="I44" s="3">
         <v>3800</v>
       </c>
       <c r="J44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K44" s="3">
         <v>3400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4100</v>
-      </c>
-      <c r="L44" s="3">
-        <v>3800</v>
       </c>
       <c r="M44" s="3">
         <v>3800</v>
       </c>
       <c r="N44" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O44" s="3">
         <v>3200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>800</v>
-      </c>
-      <c r="T44" s="3">
-        <v>600</v>
       </c>
       <c r="U44" s="3">
         <v>600</v>
       </c>
       <c r="V44" s="3">
+        <v>600</v>
+      </c>
+      <c r="W44" s="3">
         <v>500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>300</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>500</v>
       </c>
       <c r="AD44" s="3">
         <v>500</v>
       </c>
       <c r="AE44" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF44" s="3">
         <v>600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
+        <v>600</v>
+      </c>
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
-        <v>500</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>800</v>
       </c>
       <c r="N45" s="3">
         <v>800</v>
       </c>
       <c r="O45" s="3">
+        <v>800</v>
+      </c>
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4126,123 +4228,126 @@
         <v>2300</v>
       </c>
       <c r="E46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F46" s="3">
         <v>3600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>11500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,91 +4424,94 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>400</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>500</v>
       </c>
       <c r="R48" s="3">
         <v>500</v>
       </c>
       <c r="S48" s="3">
+        <v>500</v>
+      </c>
+      <c r="T48" s="3">
         <v>600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>300</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>400</v>
       </c>
       <c r="AC48" s="3">
         <v>400</v>
       </c>
       <c r="AD48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AE48" s="3">
         <v>500</v>
@@ -4412,33 +4520,36 @@
         <v>500</v>
       </c>
       <c r="AG48" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AH48" s="3">
         <v>400</v>
       </c>
       <c r="AI48" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>19</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>2500</v>
-      </c>
-      <c r="H49" s="3">
-        <v>2600</v>
       </c>
       <c r="I49" s="3">
         <v>2600</v>
@@ -4447,19 +4558,19 @@
         <v>2600</v>
       </c>
       <c r="K49" s="3">
-        <v>9500</v>
+        <v>2600</v>
       </c>
       <c r="L49" s="3">
         <v>9500</v>
       </c>
       <c r="M49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="N49" s="3">
         <v>9600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9700</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>19</v>
@@ -4473,8 +4584,8 @@
       <c r="S49" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4750,7 +4870,7 @@
         <v>500</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
@@ -4759,7 +4879,7 @@
         <v>200</v>
       </c>
       <c r="N52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>500</v>
@@ -4795,7 +4915,7 @@
         <v>500</v>
       </c>
       <c r="Z52" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AA52" s="3">
         <v>600</v>
@@ -4816,16 +4936,19 @@
         <v>600</v>
       </c>
       <c r="AG52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH52" s="3">
         <v>700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,8 +5048,11 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4934,100 +5060,103 @@
         <v>3900</v>
       </c>
       <c r="E54" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F54" s="3">
         <v>5400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,28 +5230,29 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1100</v>
       </c>
       <c r="F57" s="3">
         <v>1100</v>
       </c>
       <c r="G57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1100</v>
       </c>
       <c r="J57" s="3">
         <v>1100</v>
@@ -5130,102 +5261,105 @@
         <v>1100</v>
       </c>
       <c r="L57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>600</v>
       </c>
       <c r="AA57" s="3">
         <v>600</v>
       </c>
       <c r="AB57" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AC57" s="3">
         <v>300</v>
       </c>
       <c r="AD57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F58" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="G58" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="H58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>19</v>
+        <v>1800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5237,10 +5371,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>19</v>
@@ -5248,32 +5382,32 @@
       <c r="Q58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3000</v>
       </c>
-      <c r="X58" s="3" t="s">
+      <c r="Y58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>19</v>
@@ -5284,8 +5418,8 @@
       <c r="AC58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5302,64 +5436,67 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1700</v>
+        <v>800</v>
       </c>
       <c r="E59" s="3">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="F59" s="3">
+        <v>900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="G59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>3300</v>
-      </c>
       <c r="J59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K59" s="3">
         <v>3200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>2200</v>
       </c>
       <c r="Q59" s="3">
         <v>2200</v>
       </c>
       <c r="R59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="S59" s="3">
         <v>2500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2500</v>
-      </c>
-      <c r="U59" s="3">
-        <v>2700</v>
       </c>
       <c r="V59" s="3">
         <v>2700</v>
@@ -5368,167 +5505,173 @@
         <v>2700</v>
       </c>
       <c r="X59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Y59" s="3">
         <v>3000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4300</v>
-      </c>
-      <c r="K60" s="3">
-        <v>3700</v>
       </c>
       <c r="L60" s="3">
         <v>3700</v>
       </c>
       <c r="M60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N60" s="3">
         <v>4800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4700</v>
-      </c>
-      <c r="AG60" s="3">
-        <v>4300</v>
       </c>
       <c r="AH60" s="3">
         <v>4300</v>
       </c>
       <c r="AI60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5570,14 +5713,14 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>2800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1200</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5605,109 +5748,115 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" s="3">
+        <v>200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>300</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O62" s="3">
+        <v>10400</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>100</v>
+      </c>
+      <c r="T62" s="3">
+        <v>200</v>
+      </c>
+      <c r="U62" s="3">
+        <v>8000</v>
+      </c>
+      <c r="V62" s="3">
+        <v>4300</v>
+      </c>
+      <c r="W62" s="3">
+        <v>4600</v>
+      </c>
+      <c r="X62" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="AC62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>4900</v>
-      </c>
-      <c r="L62" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="N62" s="3">
-        <v>10400</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3">
-        <v>100</v>
-      </c>
-      <c r="S62" s="3">
-        <v>200</v>
-      </c>
-      <c r="T62" s="3">
-        <v>8000</v>
-      </c>
-      <c r="U62" s="3">
-        <v>4300</v>
-      </c>
-      <c r="V62" s="3">
-        <v>4600</v>
-      </c>
-      <c r="W62" s="3">
-        <v>4800</v>
-      </c>
-      <c r="X62" s="3">
-        <v>2100</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>600</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>900</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4100</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>4000</v>
       </c>
       <c r="AH62" s="3">
         <v>4000</v>
       </c>
       <c r="AI62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4400</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>4300</v>
       </c>
       <c r="AB66" s="3">
         <v>4300</v>
       </c>
       <c r="AC66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AD66" s="3">
         <v>5000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8900</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>8300</v>
       </c>
       <c r="AH66" s="3">
         <v>8300</v>
       </c>
       <c r="AI66" s="3">
+        <v>8300</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6358,25 +6526,25 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>1500</v>
-      </c>
-      <c r="F70" s="3">
-        <v>2000</v>
       </c>
       <c r="G70" s="3">
         <v>2000</v>
       </c>
       <c r="H70" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I70" s="3">
         <v>2100</v>
-      </c>
-      <c r="I70" s="3">
-        <v>3000</v>
       </c>
       <c r="J70" s="3">
         <v>3000</v>
       </c>
       <c r="K70" s="3">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L70" s="3">
         <v>600</v>
@@ -6385,11 +6553,11 @@
         <v>600</v>
       </c>
       <c r="N70" s="3">
+        <v>600</v>
+      </c>
+      <c r="O70" s="3">
         <v>700</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -6412,11 +6580,11 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>600</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-182200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-180000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-178400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-174800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-165700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-163900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-159900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-158200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-149900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-144200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-142000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-141900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-141700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-139400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-137600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-136100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-134300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-131100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-126600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-125000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-122300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-122100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-119500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-115000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-113700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-112200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-110600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-111100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-111900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-109400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-107700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-103700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-102000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
-        <v>-3600</v>
-      </c>
       <c r="F81" s="3">
-        <v>-9200</v>
+        <v>-3200</v>
       </c>
       <c r="G81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="S81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="W81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-4000</v>
       </c>
-      <c r="I81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="AI81" s="3">
         <v>-1600</v>
       </c>
-      <c r="V81" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>800</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,19 +7599,20 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -7422,10 +7621,10 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -7440,7 +7639,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -7476,13 +7675,13 @@
         <v>0</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB83" s="3">
         <v>100</v>
       </c>
       <c r="AC83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,52 +8221,55 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1700</v>
       </c>
       <c r="L89" s="3">
         <v>-1700</v>
       </c>
       <c r="M89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N89" s="3">
         <v>-2100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-1400</v>
       </c>
       <c r="R89" s="3">
         <v>-1400</v>
@@ -8061,55 +8278,58 @@
         <v>-1400</v>
       </c>
       <c r="T89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="U89" s="3">
         <v>-1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8365,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8172,11 +8393,11 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -8195,8 +8416,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>19</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>19</v>
@@ -8204,8 +8425,8 @@
       <c r="U91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -8232,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
@@ -8244,10 +8465,13 @@
         <v>-100</v>
       </c>
       <c r="AI91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,8 +8675,11 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8457,11 +8687,11 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>1100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -8475,20 +8705,20 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-12000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -8535,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
@@ -8547,10 +8777,13 @@
         <v>-100</v>
       </c>
       <c r="AI94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,80 +9233,83 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
-        <v>-800</v>
-      </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K100" s="3">
         <v>3000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>14800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1800</v>
       </c>
-      <c r="Q100" s="3" t="s">
+      <c r="R100" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>6000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3000</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -9071,51 +9317,54 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>5600</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>100</v>
       </c>
       <c r="AE100" s="3">
         <v>100</v>
       </c>
       <c r="AF100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>5900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>NBY</t>
   </si>
@@ -656,264 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F8" s="3">
         <v>2400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O8" s="3">
         <v>3700</v>
       </c>
-      <c r="H8" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="P8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R8" s="3">
         <v>2300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="S8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="T8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AC8" s="3">
         <v>3600</v>
       </c>
-      <c r="L8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3700</v>
-      </c>
-      <c r="N8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2600</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>4800</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="S8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="T8" s="3">
-        <v>2200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>4000</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="W8" s="3">
-        <v>1700</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>3600</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>6300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4100</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>4100</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>3700</v>
       </c>
       <c r="AI8" s="3">
         <v>4100</v>
       </c>
       <c r="AJ8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AL8" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>800</v>
+      <c r="D9" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E9" s="3">
         <v>800</v>
@@ -922,64 +935,64 @@
         <v>800</v>
       </c>
       <c r="G9" s="3">
-        <v>1900</v>
+        <v>800</v>
       </c>
       <c r="H9" s="3">
         <v>800</v>
       </c>
       <c r="I9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>800</v>
+      </c>
+      <c r="K9" s="3">
         <v>1800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1900</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M9" s="3">
-        <v>1800</v>
       </c>
       <c r="N9" s="3">
         <v>1500</v>
       </c>
       <c r="O9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1500</v>
-      </c>
-      <c r="R9" s="3">
-        <v>500</v>
-      </c>
-      <c r="S9" s="3">
-        <v>800</v>
       </c>
       <c r="T9" s="3">
         <v>500</v>
       </c>
       <c r="U9" s="3">
+        <v>800</v>
+      </c>
+      <c r="V9" s="3">
+        <v>500</v>
+      </c>
+      <c r="W9" s="3">
         <v>2000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>400</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>300</v>
       </c>
       <c r="AA9" s="3">
         <v>400</v>
@@ -988,135 +1001,147 @@
         <v>300</v>
       </c>
       <c r="AC9" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AD9" s="3">
         <v>300</v>
       </c>
       <c r="AE9" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG9" s="3">
         <v>1000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>700</v>
-      </c>
-      <c r="AH9" s="3">
-        <v>600</v>
-      </c>
-      <c r="AI9" s="3">
-        <v>800</v>
       </c>
       <c r="AJ9" s="3">
         <v>600</v>
       </c>
+      <c r="AK9" s="3">
+        <v>800</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>600</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1800</v>
       </c>
-      <c r="G10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J10" s="3">
         <v>1700</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1600</v>
       </c>
       <c r="K10" s="3">
         <v>1700</v>
       </c>
       <c r="L10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N10" s="3">
         <v>2300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1100</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>1400</v>
       </c>
       <c r="Z10" s="3">
         <v>1200</v>
       </c>
       <c r="AA10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC10" s="3">
         <v>3200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>5300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>3600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>3400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>3100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,13 +1178,15 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>0</v>
+      <c r="D12" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -1180,14 +1207,14 @@
         <v>0</v>
       </c>
       <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
       <c r="N12" s="3">
         <v>0</v>
       </c>
@@ -1207,17 +1234,17 @@
         <v>0</v>
       </c>
       <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>100</v>
       </c>
-      <c r="V12" s="3">
-        <v>0</v>
-      </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
       <c r="X12" s="3">
         <v>0</v>
       </c>
@@ -1225,13 +1252,13 @@
         <v>0</v>
       </c>
       <c r="Z12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
         <v>100</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>0</v>
       </c>
       <c r="AC12" s="3">
         <v>100</v>
@@ -1243,7 +1270,7 @@
         <v>100</v>
       </c>
       <c r="AF12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="3">
         <v>100</v>
@@ -1252,13 +1279,19 @@
         <v>100</v>
       </c>
       <c r="AI12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK12" s="3">
         <v>200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,26 +1394,32 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
@@ -1388,14 +1427,14 @@
         <v>19</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="3">
         <v>6700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>19</v>
       </c>
@@ -1405,53 +1444,53 @@
       <c r="P14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>19</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>100</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1465,8 +1504,14 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1480,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1569,8 +1614,14 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1655,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4200</v>
       </c>
-      <c r="G17" s="3">
-        <v>4500</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J17" s="3">
         <v>3200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>13100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>5800</v>
-      </c>
-      <c r="N17" s="3">
-        <v>5700</v>
       </c>
       <c r="O17" s="3">
         <v>5800</v>
       </c>
       <c r="P17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="R17" s="3">
         <v>4600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>8100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>5600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>5200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>5000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>5300</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>5900</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>6300</v>
       </c>
       <c r="AG17" s="3">
         <v>5900</v>
       </c>
       <c r="AH17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>7500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-9500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1850,25 +1915,27 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>19</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>800</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="I20" s="3">
         <v>200</v>
@@ -1877,26 +1944,26 @@
         <v>19</v>
       </c>
       <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>3100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1904,191 +1971,203 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-3400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>500</v>
       </c>
       <c r="AD20" s="3">
         <v>300</v>
       </c>
       <c r="AE20" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG20" s="3">
         <v>400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="T21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="W21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="X21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-1500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="AF21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-1700</v>
       </c>
-      <c r="T21" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="AJ21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AK21" s="3">
         <v>-1600</v>
       </c>
-      <c r="W21" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="X21" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>800</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AH21" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="3">
-        <v>700</v>
       </c>
       <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>19</v>
+      <c r="J22" s="3">
+        <v>700</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2102,11 +2181,11 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>19</v>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>19</v>
@@ -2120,26 +2199,26 @@
       <c r="V22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y22" s="3">
         <v>300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2162,112 +2241,124 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1400</v>
       </c>
       <c r="I23" s="3">
         <v>-1700</v>
       </c>
       <c r="J23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8200</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-2200</v>
       </c>
       <c r="N23" s="3">
         <v>-100</v>
       </c>
       <c r="O23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-4500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2292,11 +2383,11 @@
       <c r="J24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2349,18 +2440,18 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>19</v>
+      <c r="AD24" s="3">
+        <v>0</v>
       </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
         <v>0</v>
       </c>
@@ -2370,8 +2461,14 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1400</v>
       </c>
       <c r="I26" s="3">
         <v>-1700</v>
       </c>
       <c r="J26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-8200</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-2200</v>
       </c>
       <c r="N26" s="3">
         <v>-100</v>
       </c>
       <c r="O26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-4500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>13300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-4500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>13300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,43 +2901,49 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-400</v>
-      </c>
       <c r="I29" s="3">
-        <v>-300</v>
+        <v>-2400</v>
       </c>
       <c r="J29" s="3">
         <v>-400</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="K29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L29" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2854,33 +2975,33 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>19</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>19</v>
       </c>
@@ -2890,8 +3011,14 @@
       <c r="AJ29" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,25 +3231,31 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>19</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="I32" s="3">
         <v>-200</v>
@@ -3125,26 +3264,26 @@
         <v>19</v>
       </c>
       <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-3100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3152,162 +3291,174 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>3400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-500</v>
       </c>
       <c r="AD32" s="3">
         <v>-300</v>
       </c>
       <c r="AE32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-8200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-4500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-8200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-4500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3870,120 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>400</v>
+      </c>
+      <c r="F41" s="3">
         <v>800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1800</v>
       </c>
-      <c r="G41" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J41" s="3">
         <v>3500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>10300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>10500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>12000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>13400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>8800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>6900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>9000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>5200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>6800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>8300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>3200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>6100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>5700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>7400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,94 +4086,100 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>700</v>
+      <c r="D43" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E43" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F43" s="3">
         <v>700</v>
       </c>
       <c r="G43" s="3">
+        <v>500</v>
+      </c>
+      <c r="H43" s="3">
+        <v>700</v>
+      </c>
+      <c r="I43" s="3">
+        <v>700</v>
+      </c>
+      <c r="J43" s="3">
+        <v>900</v>
+      </c>
+      <c r="K43" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N43" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
-        <v>900</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="S43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AD43" s="3">
         <v>2600</v>
       </c>
-      <c r="J43" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="AE43" s="3">
         <v>2000</v>
-      </c>
-      <c r="L43" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N43" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O43" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P43" s="3">
-        <v>800</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>1200</v>
-      </c>
-      <c r="R43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="S43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="X43" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>2400</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>3400</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>2600</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>2200</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>3600</v>
       </c>
       <c r="AF43" s="3">
         <v>2200</v>
@@ -4003,90 +4188,96 @@
         <v>3600</v>
       </c>
       <c r="AH43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>2300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="3">
+        <v>800</v>
+      </c>
+      <c r="F44" s="3">
         <v>500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>700</v>
       </c>
-      <c r="G44" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
+        <v>500</v>
+      </c>
+      <c r="J44" s="3">
         <v>3600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>4100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>900</v>
-      </c>
-      <c r="S44" s="3">
-        <v>600</v>
-      </c>
-      <c r="T44" s="3">
-        <v>800</v>
       </c>
       <c r="U44" s="3">
         <v>600</v>
       </c>
       <c r="V44" s="3">
+        <v>800</v>
+      </c>
+      <c r="W44" s="3">
         <v>600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y44" s="3">
         <v>500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>700</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>300</v>
       </c>
       <c r="AB44" s="3">
         <v>400</v>
@@ -4095,36 +4286,42 @@
         <v>300</v>
       </c>
       <c r="AD44" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF44" s="3">
         <v>500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>100</v>
+      <c r="D45" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -4136,195 +4333,207 @@
         <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
       </c>
       <c r="K45" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="L45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M45" s="3">
         <v>600</v>
       </c>
       <c r="N45" s="3">
+        <v>500</v>
+      </c>
+      <c r="O45" s="3">
+        <v>600</v>
+      </c>
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>800</v>
       </c>
       <c r="S45" s="3">
         <v>600</v>
       </c>
       <c r="T45" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="U45" s="3">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="V45" s="3">
         <v>700</v>
       </c>
       <c r="W45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X45" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1700</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>900</v>
       </c>
       <c r="AH45" s="3">
         <v>1000</v>
       </c>
       <c r="AI45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK45" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F46" s="3">
         <v>2300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>7200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>11300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>10600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>9500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>12500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>13200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>11500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>12800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>13100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>14200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>16000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>11900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>9400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>12500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>7500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>7100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>8600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>9500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>10800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>12800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>9000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>9900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>11000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>11500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>14500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,11 +4558,11 @@
       <c r="J47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4427,112 +4636,124 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>400</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>500</v>
       </c>
       <c r="AG48" s="3">
         <v>500</v>
       </c>
       <c r="AH48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4549,35 +4770,35 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>2500</v>
-      </c>
-      <c r="I49" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>2600</v>
       </c>
       <c r="K49" s="3">
         <v>2600</v>
       </c>
       <c r="L49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N49" s="3">
         <v>9500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>9500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>9600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>9700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>19</v>
       </c>
@@ -4587,11 +4808,11 @@
       <c r="T49" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -4635,8 +4856,14 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +5076,14 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4873,19 +5112,19 @@
         <v>500</v>
       </c>
       <c r="L52" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="M52" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
       </c>
       <c r="O52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="P52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="Q52" s="3">
         <v>500</v>
@@ -4918,10 +5157,10 @@
         <v>500</v>
       </c>
       <c r="AA52" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB52" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AC52" s="3">
         <v>600</v>
@@ -4939,16 +5178,22 @@
         <v>600</v>
       </c>
       <c r="AH52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F54" s="3">
         <v>3900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>9000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>12900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>16000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>14800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>16400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>22400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>21500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>24800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>24000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>12200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>13600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>14100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>15200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>17100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>13300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>9500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>11200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>14600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>9900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>9700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>9400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>10400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>11700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>13800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>10100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>11100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>12100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>12700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,142 +5490,150 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
+        <v>900</v>
+      </c>
+      <c r="K57" s="3">
         <v>1500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1100</v>
       </c>
       <c r="L57" s="3">
         <v>1100</v>
       </c>
       <c r="M57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>800</v>
-      </c>
-      <c r="S57" s="3">
-        <v>300</v>
       </c>
       <c r="T57" s="3">
         <v>800</v>
       </c>
       <c r="U57" s="3">
+        <v>300</v>
+      </c>
+      <c r="V57" s="3">
+        <v>800</v>
+      </c>
+      <c r="W57" s="3">
         <v>1300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>300</v>
-      </c>
-      <c r="X57" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>400</v>
       </c>
       <c r="Z57" s="3">
         <v>500</v>
       </c>
       <c r="AA57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="G58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J58" s="3">
         <v>1800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5374,58 +5641,58 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB58" s="3">
         <v>1000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>19</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
@@ -5439,246 +5706,264 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
-        <v>900</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>700</v>
+      </c>
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2200</v>
-      </c>
-      <c r="S59" s="3">
-        <v>2500</v>
-      </c>
-      <c r="T59" s="3">
-        <v>2100</v>
       </c>
       <c r="U59" s="3">
         <v>2500</v>
       </c>
       <c r="V59" s="3">
-        <v>2700</v>
+        <v>2100</v>
       </c>
       <c r="W59" s="3">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="X59" s="3">
         <v>2700</v>
       </c>
       <c r="Y59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AA59" s="3">
         <v>3000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>3900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>3300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>2900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>4500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>4900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>3800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>3500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F60" s="3">
         <v>2000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>5500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>5700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>6300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>5400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>3400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>3100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>3200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>5000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>5300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>4700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>4300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>700</v>
+      </c>
+      <c r="F61" s="3">
         <v>800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5716,17 +6001,17 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>2800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1200</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5751,8 +6036,14 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5762,101 +6053,107 @@
       <c r="E62" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>300</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>4900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>10400</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>8000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>4600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>4800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>2500</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>4100</v>
       </c>
       <c r="AH62" s="3">
         <v>4000</v>
       </c>
       <c r="AI62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AL62" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F66" s="3">
         <v>2800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>5800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>8600</v>
       </c>
       <c r="M66" s="3">
         <v>5800</v>
       </c>
       <c r="N66" s="3">
+        <v>8600</v>
+      </c>
+      <c r="O66" s="3">
+        <v>5800</v>
+      </c>
+      <c r="P66" s="3">
         <v>7000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>13800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>12300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>10200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>11100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>8200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>8600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>4400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>4300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>4300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>5000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>7500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>9200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>8900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>8300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6529,41 +6864,41 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>1500</v>
       </c>
-      <c r="G70" s="3">
+      <c r="I70" s="3">
         <v>2000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="J70" s="3">
         <v>2000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="K70" s="3">
         <v>2100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="L70" s="3">
         <v>3000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="M70" s="3">
         <v>3000</v>
-      </c>
-      <c r="L70" s="3">
-        <v>600</v>
-      </c>
-      <c r="M70" s="3">
-        <v>600</v>
       </c>
       <c r="N70" s="3">
         <v>600</v>
       </c>
       <c r="O70" s="3">
+        <v>600</v>
+      </c>
+      <c r="P70" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q70" s="3">
         <v>700</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -6583,14 +6918,14 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>600</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -6621,8 +6956,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +7066,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-175800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-183500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-182200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-180000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-178400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-174800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-165700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-163900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-159900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-158200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-149900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-144200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-142000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-141900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-141700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-139400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-137600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-136100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-134300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-131100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-126600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-125000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-122300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-122100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-119500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-115000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-113700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-112200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-110600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-111100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-111900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-109400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-107700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-103700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-102000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F76" s="3">
         <v>1100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-1300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>15200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>17100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>9500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>11200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>11000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>12300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>13900</v>
-      </c>
-      <c r="U76" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V76" s="3">
-        <v>-300</v>
       </c>
       <c r="W76" s="3">
         <v>1000</v>
       </c>
       <c r="X76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z76" s="3">
         <v>2900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>6100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>7400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>8900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>2600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>3200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>4400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-8200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-4500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,37 +7995,39 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -7642,10 +8039,10 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -7678,17 +8075,17 @@
         <v>0</v>
       </c>
       <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
         <v>100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>100</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
@@ -7704,8 +8101,14 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1800</v>
       </c>
-      <c r="G89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-1400</v>
       </c>
       <c r="T89" s="3">
         <v>-1400</v>
       </c>
       <c r="U89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="W89" s="3">
         <v>-1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,13 +8805,15 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -8396,14 +8837,14 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -8419,20 +8860,20 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>19</v>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -8456,10 +8897,10 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH91" s="3">
         <v>-100</v>
@@ -8468,10 +8909,16 @@
         <v>-100</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,26 +9131,32 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>1100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -8708,23 +9167,23 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-12000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -8768,10 +9227,10 @@
         <v>0</v>
       </c>
       <c r="AF94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH94" s="3">
         <v>-100</v>
@@ -8780,10 +9239,16 @@
         <v>-100</v>
       </c>
       <c r="AJ94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9285,10 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,11 +9313,11 @@
       <c r="J96" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8924,8 +9391,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9721,124 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>500</v>
+      </c>
+      <c r="F100" s="3">
         <v>2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-500</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>-600</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M100" s="3">
         <v>3000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>14800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>6000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>4100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>6900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>2500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>3000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>5600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>100</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,11 +9863,11 @@
       <c r="J101" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9444,108 +9941,120 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="E102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K102" s="3">
+        <v>700</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="M102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="P102" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="R102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="S102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="T102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="U102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="V102" s="3">
+        <v>4600</v>
+      </c>
+      <c r="W102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="X102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I102" s="3">
-        <v>700</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="AC102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="AE102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AH102" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-1700</v>
       </c>
-      <c r="N102" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="T102" s="3">
-        <v>4600</v>
-      </c>
-      <c r="U102" s="3">
-        <v>3100</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="AJ102" s="3">
         <v>-2100</v>
       </c>
-      <c r="X102" s="3">
-        <v>5400</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="AB102" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AE102" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="AF102" s="3">
-        <v>400</v>
-      </c>
-      <c r="AG102" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AH102" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>5900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>NBY</t>
   </si>
@@ -656,280 +656,287 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="3">
         <v>2300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2400</v>
       </c>
       <c r="G8" s="3">
         <v>2400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="O8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="P8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R8" s="3">
         <v>2600</v>
       </c>
-      <c r="I8" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K8" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="S8" s="3">
         <v>2300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="T8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="U8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD8" s="3">
         <v>3600</v>
       </c>
-      <c r="N8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="O8" s="3">
-        <v>3700</v>
-      </c>
-      <c r="P8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>2600</v>
-      </c>
-      <c r="R8" s="3">
-        <v>2300</v>
-      </c>
-      <c r="S8" s="3">
-        <v>4800</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="V8" s="3">
-        <v>2200</v>
-      </c>
-      <c r="W8" s="3">
-        <v>4000</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>3600</v>
-      </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6300</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>4100</v>
       </c>
       <c r="AI8" s="3">
         <v>4100</v>
       </c>
       <c r="AJ8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AK8" s="3">
         <v>3700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="3">
-        <v>800</v>
+      <c r="E9" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="F9" s="3">
         <v>800</v>
@@ -937,211 +944,217 @@
       <c r="G9" s="3">
         <v>800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K9" s="3">
         <v>800</v>
       </c>
-      <c r="I9" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M9" s="3">
+        <v>700</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S9" s="3">
+        <v>700</v>
+      </c>
+      <c r="T9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U9" s="3">
+        <v>500</v>
+      </c>
+      <c r="V9" s="3">
         <v>800</v>
       </c>
-      <c r="K9" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L9" s="3">
-        <v>700</v>
-      </c>
-      <c r="M9" s="3">
-        <v>1900</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1800</v>
-      </c>
-      <c r="P9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1200</v>
-      </c>
-      <c r="R9" s="3">
-        <v>700</v>
-      </c>
-      <c r="S9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="W9" s="3">
         <v>500</v>
       </c>
-      <c r="U9" s="3">
-        <v>800</v>
-      </c>
-      <c r="V9" s="3">
-        <v>500</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2000</v>
-      </c>
-      <c r="X9" s="3">
-        <v>600</v>
       </c>
       <c r="Y9" s="3">
         <v>600</v>
       </c>
       <c r="Z9" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AA9" s="3">
         <v>400</v>
       </c>
       <c r="AB9" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC9" s="3">
         <v>300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3">
         <v>1500</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1600</v>
       </c>
       <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="H10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="3">
         <v>1100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1700</v>
       </c>
       <c r="K10" s="3">
         <v>1700</v>
       </c>
       <c r="L10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M10" s="3">
         <v>1600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1213,11 +1227,11 @@
         <v>0</v>
       </c>
       <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
       <c r="O12" s="3">
         <v>0</v>
       </c>
@@ -1240,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="V12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W12" s="3">
         <v>100</v>
       </c>
       <c r="X12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y12" s="3">
         <v>0</v>
@@ -1258,22 +1272,22 @@
         <v>0</v>
       </c>
       <c r="AB12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="3">
         <v>100</v>
       </c>
       <c r="AD12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3">
         <v>100</v>
       </c>
-      <c r="AF12" s="3">
-        <v>0</v>
-      </c>
       <c r="AG12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH12" s="3">
         <v>100</v>
@@ -1285,13 +1299,16 @@
         <v>100</v>
       </c>
       <c r="AK12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL12" s="3">
         <v>200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,44 +1417,47 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>800</v>
-      </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="3">
         <v>6700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>19</v>
       </c>
@@ -1450,8 +1470,8 @@
       <c r="R14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1459,8 +1479,8 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>19</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>19</v>
@@ -1468,8 +1488,8 @@
       <c r="X14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1478,11 +1498,11 @@
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>19</v>
       </c>
@@ -1492,8 +1512,8 @@
       <c r="AF14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,129 +1683,133 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3500</v>
       </c>
       <c r="G17" s="3">
         <v>3500</v>
       </c>
       <c r="H17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="M17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N17" s="3">
+        <v>13100</v>
+      </c>
+      <c r="O17" s="3">
+        <v>4300</v>
+      </c>
+      <c r="P17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="R17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="S17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="T17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="U17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="V17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W17" s="3">
         <v>4200</v>
       </c>
-      <c r="I17" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="X17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AB17" s="3">
         <v>3200</v>
       </c>
-      <c r="K17" s="3">
-        <v>4600</v>
-      </c>
-      <c r="L17" s="3">
-        <v>3700</v>
-      </c>
-      <c r="M17" s="3">
-        <v>13100</v>
-      </c>
-      <c r="N17" s="3">
-        <v>4300</v>
-      </c>
-      <c r="O17" s="3">
-        <v>5800</v>
-      </c>
-      <c r="P17" s="3">
-        <v>5700</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>5800</v>
-      </c>
-      <c r="R17" s="3">
-        <v>4600</v>
-      </c>
-      <c r="S17" s="3">
-        <v>8100</v>
-      </c>
-      <c r="T17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="U17" s="3">
-        <v>3600</v>
-      </c>
-      <c r="V17" s="3">
-        <v>4200</v>
-      </c>
-      <c r="W17" s="3">
-        <v>5100</v>
-      </c>
-      <c r="X17" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>3900</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1100</v>
       </c>
       <c r="G18" s="3">
         <v>-1100</v>
@@ -1788,97 +1818,100 @@
         <v>-1600</v>
       </c>
       <c r="I18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AK18" s="3">
-        <v>-2100</v>
       </c>
       <c r="AL18" s="3">
         <v>-2100</v>
       </c>
+      <c r="AM18" s="3">
+        <v>-2100</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1928,45 +1962,45 @@
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>2200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1977,200 +2011,206 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-300</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1200</v>
       </c>
-      <c r="H21" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1300</v>
       </c>
       <c r="L21" s="3">
         <v>-1300</v>
       </c>
       <c r="M21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N21" s="3">
         <v>-8100</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-2000</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2187,8 +2227,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>19</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>19</v>
@@ -2205,23 +2245,23 @@
       <c r="X22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Y22" s="3">
-        <v>300</v>
+      <c r="Y22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="Z22" s="3">
         <v>300</v>
       </c>
       <c r="AA22" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB22" s="3">
         <v>400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2247,118 +2287,124 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="T23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="U23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="H23" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="Z23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-1700</v>
       </c>
-      <c r="J23" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="AK23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AL23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y23" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>800</v>
-      </c>
-      <c r="AH23" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AI23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AJ23" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AK23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2389,8 +2435,8 @@
       <c r="L24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2446,15 +2492,15 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-12500</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
         <v>0</v>
       </c>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="T26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="U26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="W26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="Z26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>13300</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-1700</v>
       </c>
-      <c r="J26" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="AK26" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AL26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y26" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>13300</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AI26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AJ26" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AK26" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E27" s="3">
         <v>7700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>13300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,46 +2965,49 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>11000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>100</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-100</v>
+        <v>600</v>
       </c>
       <c r="I29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-400</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2981,17 +3042,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>19</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>19</v>
+      <c r="AC29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>19</v>
@@ -2999,12 +3060,12 @@
       <c r="AF29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-12500</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>19</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3248,45 +3318,45 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3297,168 +3367,174 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>300</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E33" s="3">
         <v>7700</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-1200</v>
       </c>
       <c r="F33" s="3">
         <v>-1200</v>
       </c>
       <c r="G33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E35" s="3">
         <v>7700</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-1200</v>
       </c>
       <c r="F35" s="3">
         <v>-1200</v>
       </c>
       <c r="G35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E41" s="3">
         <v>8500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>400</v>
-      </c>
-      <c r="F41" s="3">
-        <v>800</v>
       </c>
       <c r="G41" s="3">
         <v>800</v>
       </c>
       <c r="H41" s="3">
+        <v>800</v>
+      </c>
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5400</v>
-      </c>
-      <c r="N41" s="3">
-        <v>3900</v>
       </c>
       <c r="O41" s="3">
         <v>3900</v>
       </c>
       <c r="P41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="Q41" s="3">
         <v>5600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>13400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>7400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>9500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,239 +4182,248 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>19</v>
+      <c r="D43" s="3">
+        <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
-      </c>
-      <c r="H43" s="3">
-        <v>700</v>
       </c>
       <c r="I43" s="3">
         <v>700</v>
       </c>
       <c r="J43" s="3">
+        <v>700</v>
+      </c>
+      <c r="K43" s="3">
         <v>900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1000</v>
-      </c>
-      <c r="U43" s="3">
-        <v>1100</v>
       </c>
       <c r="V43" s="3">
         <v>1100</v>
       </c>
       <c r="W43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X43" s="3">
         <v>1400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>1500</v>
       </c>
       <c r="AA43" s="3">
         <v>1500</v>
       </c>
       <c r="AB43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AC43" s="3">
         <v>2400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2300</v>
-      </c>
-      <c r="AK43" s="3">
-        <v>2100</v>
       </c>
       <c r="AL43" s="3">
         <v>2100</v>
       </c>
+      <c r="AM43" s="3">
+        <v>2100</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>500</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="3">
         <v>800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>700</v>
       </c>
       <c r="H44" s="3">
         <v>700</v>
       </c>
       <c r="I44" s="3">
+        <v>700</v>
+      </c>
+      <c r="J44" s="3">
         <v>500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4100</v>
-      </c>
-      <c r="O44" s="3">
-        <v>3800</v>
       </c>
       <c r="P44" s="3">
         <v>3800</v>
       </c>
       <c r="Q44" s="3">
+        <v>3800</v>
+      </c>
+      <c r="R44" s="3">
         <v>3200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>800</v>
-      </c>
-      <c r="W44" s="3">
-        <v>600</v>
       </c>
       <c r="X44" s="3">
         <v>600</v>
       </c>
       <c r="Y44" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z44" s="3">
         <v>500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>300</v>
-      </c>
-      <c r="AF44" s="3">
-        <v>500</v>
       </c>
       <c r="AG44" s="3">
         <v>500</v>
       </c>
       <c r="AH44" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI44" s="3">
         <v>600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>19</v>
+      <c r="D45" s="3">
+        <v>100</v>
       </c>
       <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
@@ -4333,207 +4432,213 @@
         <v>100</v>
       </c>
       <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3">
         <v>2800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>800</v>
       </c>
       <c r="Q45" s="3">
         <v>800</v>
       </c>
       <c r="R45" s="3">
+        <v>800</v>
+      </c>
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E46" s="3">
         <v>9000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1900</v>
-      </c>
-      <c r="F46" s="3">
-        <v>2300</v>
       </c>
       <c r="G46" s="3">
         <v>2300</v>
       </c>
       <c r="H46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I46" s="3">
         <v>3600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>9900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>11500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>14500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4642,100 +4747,103 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>400</v>
-      </c>
-      <c r="T48" s="3">
-        <v>500</v>
       </c>
       <c r="U48" s="3">
         <v>500</v>
       </c>
       <c r="V48" s="3">
+        <v>500</v>
+      </c>
+      <c r="W48" s="3">
         <v>600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>300</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>400</v>
       </c>
       <c r="AF48" s="3">
         <v>400</v>
       </c>
       <c r="AG48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AH48" s="3">
         <v>500</v>
@@ -4744,16 +4852,19 @@
         <v>500</v>
       </c>
       <c r="AJ48" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK48" s="3">
         <v>400</v>
       </c>
       <c r="AL48" s="3">
+        <v>400</v>
+      </c>
+      <c r="AM48" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4776,10 +4887,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>2500</v>
-      </c>
-      <c r="K49" s="3">
-        <v>2600</v>
       </c>
       <c r="L49" s="3">
         <v>2600</v>
@@ -4788,20 +4899,20 @@
         <v>2600</v>
       </c>
       <c r="N49" s="3">
-        <v>9500</v>
+        <v>2600</v>
       </c>
       <c r="O49" s="3">
         <v>9500</v>
       </c>
       <c r="P49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="Q49" s="3">
         <v>9600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>19</v>
       </c>
@@ -4814,8 +4925,8 @@
       <c r="V49" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5118,7 +5238,7 @@
         <v>500</v>
       </c>
       <c r="N52" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
@@ -5127,7 +5247,7 @@
         <v>200</v>
       </c>
       <c r="Q52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="R52" s="3">
         <v>500</v>
@@ -5163,7 +5283,7 @@
         <v>500</v>
       </c>
       <c r="AC52" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AD52" s="3">
         <v>600</v>
@@ -5184,16 +5304,19 @@
         <v>600</v>
       </c>
       <c r="AJ52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AK52" s="3">
         <v>700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E54" s="3">
         <v>9900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3400</v>
-      </c>
-      <c r="F54" s="3">
-        <v>3900</v>
       </c>
       <c r="G54" s="3">
         <v>3900</v>
       </c>
       <c r="H54" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I54" s="3">
         <v>5400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>24800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>14600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>15400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,37 +5622,38 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>900</v>
       </c>
       <c r="J57" s="3">
         <v>900</v>
       </c>
       <c r="K57" s="3">
+        <v>900</v>
+      </c>
+      <c r="L57" s="3">
         <v>1500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1100</v>
       </c>
       <c r="M57" s="3">
         <v>1100</v>
@@ -5531,79 +5662,82 @@
         <v>1100</v>
       </c>
       <c r="O57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>600</v>
       </c>
       <c r="AD57" s="3">
         <v>600</v>
       </c>
       <c r="AE57" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AF57" s="3">
         <v>300</v>
       </c>
       <c r="AG57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH57" s="3">
         <v>500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5611,32 +5745,32 @@
         <v>500</v>
       </c>
       <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5647,44 +5781,44 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>19</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>19</v>
       </c>
@@ -5694,8 +5828,8 @@
       <c r="AF58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -5712,73 +5846,76 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>19</v>
+      <c r="D59" s="3">
+        <v>300</v>
       </c>
       <c r="E59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F59" s="3">
         <v>500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>800</v>
       </c>
       <c r="G59" s="3">
         <v>800</v>
       </c>
       <c r="H59" s="3">
+        <v>800</v>
+      </c>
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1500</v>
-      </c>
-      <c r="S59" s="3">
-        <v>2200</v>
       </c>
       <c r="T59" s="3">
         <v>2200</v>
       </c>
       <c r="U59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="V59" s="3">
         <v>2500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2500</v>
-      </c>
-      <c r="X59" s="3">
-        <v>2700</v>
       </c>
       <c r="Y59" s="3">
         <v>2700</v>
@@ -5787,186 +5924,192 @@
         <v>2700</v>
       </c>
       <c r="AA59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AB59" s="3">
         <v>3000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4300</v>
-      </c>
-      <c r="N60" s="3">
-        <v>3700</v>
       </c>
       <c r="O60" s="3">
         <v>3700</v>
       </c>
       <c r="P60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Q60" s="3">
         <v>4800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4700</v>
-      </c>
-      <c r="AJ60" s="3">
-        <v>4300</v>
       </c>
       <c r="AK60" s="3">
         <v>4300</v>
       </c>
       <c r="AL60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AM60" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>500</v>
+      </c>
+      <c r="E61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -6007,14 +6150,14 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>2800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1200</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -6042,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6059,39 +6205,39 @@
       <c r="G62" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N62" s="3">
         <v>1600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10400</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
       <c r="S62" s="3">
         <v>0</v>
       </c>
@@ -6099,61 +6245,64 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4100</v>
-      </c>
-      <c r="AJ62" s="3">
-        <v>4000</v>
       </c>
       <c r="AK62" s="3">
         <v>4000</v>
       </c>
       <c r="AL62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AM62" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E66" s="3">
         <v>3700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4400</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>4300</v>
       </c>
       <c r="AE66" s="3">
         <v>4300</v>
       </c>
       <c r="AF66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AG66" s="3">
         <v>5000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8900</v>
-      </c>
-      <c r="AJ66" s="3">
-        <v>8300</v>
       </c>
       <c r="AK66" s="3">
         <v>8300</v>
       </c>
       <c r="AL66" s="3">
+        <v>8300</v>
+      </c>
+      <c r="AM66" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6870,25 +7038,25 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>1500</v>
-      </c>
-      <c r="I70" s="3">
-        <v>2000</v>
       </c>
       <c r="J70" s="3">
         <v>2000</v>
       </c>
       <c r="K70" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L70" s="3">
         <v>2100</v>
-      </c>
-      <c r="L70" s="3">
-        <v>3000</v>
       </c>
       <c r="M70" s="3">
         <v>3000</v>
       </c>
       <c r="N70" s="3">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="O70" s="3">
         <v>600</v>
@@ -6897,11 +7065,11 @@
         <v>600</v>
       </c>
       <c r="Q70" s="3">
+        <v>600</v>
+      </c>
+      <c r="R70" s="3">
         <v>700</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -6924,11 +7092,11 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>600</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-177700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-175800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-183500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-182200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-180000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-178400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-174800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-165700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-163900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-159900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-158200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-149900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-144200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-142000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-141900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-141700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-139400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-137600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-136100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-134300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-131100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-126600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-125000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-122300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-122100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-119500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-115000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-113700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-112200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-110600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-111100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-111900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-109400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-107700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-103700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-102000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E76" s="3">
         <v>6200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E81" s="3">
         <v>7700</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-1200</v>
       </c>
       <c r="F81" s="3">
         <v>-1200</v>
       </c>
       <c r="G81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,13 +8195,14 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -8012,25 +8211,25 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -8045,7 +8244,7 @@
         <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -8081,13 +8280,13 @@
         <v>0</v>
       </c>
       <c r="AD83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE83" s="3">
         <v>100</v>
       </c>
       <c r="AF83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG83" s="3">
         <v>0</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,61 +8871,64 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E89" s="3">
         <v>9700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L89" s="3">
         <v>-1800</v>
       </c>
-      <c r="I89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-1700</v>
       </c>
       <c r="O89" s="3">
         <v>-1700</v>
       </c>
       <c r="P89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-1400</v>
       </c>
       <c r="U89" s="3">
         <v>-1400</v>
@@ -8720,55 +8937,58 @@
         <v>-1400</v>
       </c>
       <c r="W89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="X89" s="3">
         <v>-1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,16 +9027,17 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -8843,11 +9064,11 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -8866,8 +9087,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>19</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>19</v>
@@ -8875,8 +9096,8 @@
       <c r="X91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -8903,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="AH91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI91" s="3">
         <v>-100</v>
@@ -8915,10 +9136,13 @@
         <v>-100</v>
       </c>
       <c r="AL91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,16 +9364,19 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -9155,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
@@ -9173,20 +9403,20 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-12000</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -9233,7 +9463,7 @@
         <v>0</v>
       </c>
       <c r="AH94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI94" s="3">
         <v>-100</v>
@@ -9245,10 +9475,13 @@
         <v>-100</v>
       </c>
       <c r="AL94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,89 +9970,92 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N100" s="3">
         <v>3000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>6000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>6900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3000</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
@@ -9817,28 +10063,31 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>5600</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>100</v>
       </c>
       <c r="AH100" s="3">
         <v>100</v>
       </c>
       <c r="AI100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
       <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3">
         <v>900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E102" s="3">
         <v>8000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>5900</v>
       </c>
     </row>
